--- a/data/Hackathon CV.xlsx
+++ b/data/Hackathon CV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sayyid/Documents/hackathon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2005BD0-02F1-824E-B9CA-9AD7AEE56613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3728205-E47B-A342-A642-B620187BAF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{9DF71BD7-8522-F64A-9F16-BDAC1601D549}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="534">
   <si>
     <t>#</t>
   </si>
@@ -1501,6 +1501,141 @@
   </si>
   <si>
     <t>sayyid,hisyam,jazli,hafidz</t>
+  </si>
+  <si>
+    <t>https://luma.com/zda76sc1?tk=f30DS9</t>
+  </si>
+  <si>
+    <t>https://github.com/sayyidkhan/zo-relationship-mapper</t>
+  </si>
+  <si>
+    <t>Suntec Tower 1</t>
+  </si>
+  <si>
+    <t>Sup</t>
+  </si>
+  <si>
+    <t>zo relationship mapper</t>
+  </si>
+  <si>
+    <t>productivity</t>
+  </si>
+  <si>
+    <t>Live career opportunity and relationship mapper powered by OpenAI and Exa</t>
+  </si>
+  <si>
+    <t>27/6/2026</t>
+  </si>
+  <si>
+    <t>Sup Build2026 Hackathon</t>
+  </si>
+  <si>
+    <t>https://ambassador.zo.space/build-challenge</t>
+  </si>
+  <si>
+    <t>https://github.com/sayyidkhan/zo-order-tracker</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Zo Order Tracker</t>
+  </si>
+  <si>
+    <t>A lightweight storefront and payment-proof order tracker for small businesses, deployed on Zo Computer.</t>
+  </si>
+  <si>
+    <t>sayyid,hong ming,bruce,aslam</t>
+  </si>
+  <si>
+    <t>Zo Computer</t>
+  </si>
+  <si>
+    <t>Zo Computer Jun 2026 Build Challenge</t>
+  </si>
+  <si>
+    <t>20 Jun - 21 Jun 2026</t>
+  </si>
+  <si>
+    <t>https://luma.com/4hx7p0vs?tk=ruRx4s</t>
+  </si>
+  <si>
+    <t>https://github.com/sayyidkhan/mums-can-build</t>
+  </si>
+  <si>
+    <t>Mums Can Build</t>
+  </si>
+  <si>
+    <t>Voice-first backend harness that turns spoken software ideas into structured Codex tasks, then coordinates a builder worker and streams progress back to the user.</t>
+  </si>
+  <si>
+    <t>SuperTeam SG,Hashed,Petani</t>
+  </si>
+  <si>
+    <t>Ralphthon SG 2026</t>
+  </si>
+  <si>
+    <t>17/5/26</t>
+  </si>
+  <si>
+    <t>1/5/2026 - 30/5/2026</t>
+  </si>
+  <si>
+    <t>Top 20, 10K USD OpenAI Credits, 2K USD Gemini Cloud Credits</t>
+  </si>
+  <si>
+    <t>UCWS 2026 (Semi-Finals)</t>
+  </si>
+  <si>
+    <t>sayyid,clarence tan</t>
+  </si>
+  <si>
+    <t>Buzo 2.0</t>
+  </si>
+  <si>
+    <t>UCWS 2026 (Finals)</t>
+  </si>
+  <si>
+    <t>13/6/2026</t>
+  </si>
+  <si>
+    <t>Buzo 2.1</t>
+  </si>
+  <si>
+    <t>https://luma.com/UCWS2026?tk=y5h4YG</t>
+  </si>
+  <si>
+    <t>8 George St, Pickering Operations Complex</t>
+  </si>
+  <si>
+    <t>Super AI Hackathon 2026</t>
+  </si>
+  <si>
+    <t>Epic Connector</t>
+  </si>
+  <si>
+    <t>SuperAI</t>
+  </si>
+  <si>
+    <t>Super AI</t>
+  </si>
+  <si>
+    <t>9/6/2026 - 11/6/2026</t>
+  </si>
+  <si>
+    <t>Movie</t>
+  </si>
+  <si>
+    <t>sayyid,mika,adora</t>
+  </si>
+  <si>
+    <t>https://github.com/sayyidkhan/agentic-vr-frontend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SceneVerse AI </t>
+  </si>
+  <si>
+    <t>Agentic AI + VR - Talk to the movie characters</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E31B418-2D71-AD42-B07B-AEB5ED36DC01}">
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="53.1640625" bestFit="1" customWidth="1"/>
@@ -1886,14 +2021,14 @@
     <col min="4" max="4" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="53.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="75.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="61" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="40.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="31.33203125" customWidth="1"/>
-    <col min="14" max="14" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="45.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="62.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="49.1640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -3707,7 +3842,7 @@
         <v>281</v>
       </c>
       <c r="C37" t="s">
-        <v>256</v>
+        <v>527</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>257</v>
@@ -5141,6 +5276,303 @@
       </c>
       <c r="P65" t="s">
         <v>482</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>512</v>
+      </c>
+      <c r="C66" t="s">
+        <v>511</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>306</v>
+      </c>
+      <c r="G66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" t="s">
+        <v>374</v>
+      </c>
+      <c r="I66" t="s">
+        <v>510</v>
+      </c>
+      <c r="J66" t="s">
+        <v>295</v>
+      </c>
+      <c r="K66" t="s">
+        <v>509</v>
+      </c>
+      <c r="L66" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" t="s">
+        <v>287</v>
+      </c>
+      <c r="N66" t="s">
+        <v>491</v>
+      </c>
+      <c r="O66" t="s">
+        <v>508</v>
+      </c>
+      <c r="P66" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>516</v>
+      </c>
+      <c r="C67" t="s">
+        <v>525</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>307</v>
+      </c>
+      <c r="G67" t="s">
+        <v>515</v>
+      </c>
+      <c r="H67" t="s">
+        <v>402</v>
+      </c>
+      <c r="I67" t="s">
+        <v>410</v>
+      </c>
+      <c r="J67" t="s">
+        <v>517</v>
+      </c>
+      <c r="K67" t="s">
+        <v>518</v>
+      </c>
+      <c r="L67" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" t="s">
+        <v>287</v>
+      </c>
+      <c r="N67" t="s">
+        <v>319</v>
+      </c>
+      <c r="O67" t="s">
+        <v>21</v>
+      </c>
+      <c r="P67" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>524</v>
+      </c>
+      <c r="C68" t="s">
+        <v>527</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E68">
+        <v>3</v>
+      </c>
+      <c r="F68" t="s">
+        <v>306</v>
+      </c>
+      <c r="G68" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" t="s">
+        <v>529</v>
+      </c>
+      <c r="I68" t="s">
+        <v>533</v>
+      </c>
+      <c r="J68" t="s">
+        <v>530</v>
+      </c>
+      <c r="K68" t="s">
+        <v>532</v>
+      </c>
+      <c r="L68" t="s">
+        <v>526</v>
+      </c>
+      <c r="M68" t="s">
+        <v>287</v>
+      </c>
+      <c r="N68" t="s">
+        <v>256</v>
+      </c>
+      <c r="O68" t="s">
+        <v>531</v>
+      </c>
+      <c r="P68" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>519</v>
+      </c>
+      <c r="C69" t="s">
+        <v>525</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>306</v>
+      </c>
+      <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" t="s">
+        <v>402</v>
+      </c>
+      <c r="I69" t="s">
+        <v>410</v>
+      </c>
+      <c r="J69" t="s">
+        <v>517</v>
+      </c>
+      <c r="K69" t="s">
+        <v>521</v>
+      </c>
+      <c r="L69" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" t="s">
+        <v>287</v>
+      </c>
+      <c r="N69" t="s">
+        <v>523</v>
+      </c>
+      <c r="O69" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>505</v>
+      </c>
+      <c r="C70" t="s">
+        <v>504</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70" t="s">
+        <v>306</v>
+      </c>
+      <c r="H70" t="s">
+        <v>494</v>
+      </c>
+      <c r="I70" t="s">
+        <v>502</v>
+      </c>
+      <c r="J70" t="s">
+        <v>503</v>
+      </c>
+      <c r="K70" t="s">
+        <v>501</v>
+      </c>
+      <c r="L70" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" t="s">
+        <v>500</v>
+      </c>
+      <c r="N70" t="s">
+        <v>319</v>
+      </c>
+      <c r="O70" t="s">
+        <v>499</v>
+      </c>
+      <c r="P70" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>497</v>
+      </c>
+      <c r="C71" t="s">
+        <v>492</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>306</v>
+      </c>
+      <c r="G71" t="s">
+        <v>21</v>
+      </c>
+      <c r="H71" t="s">
+        <v>494</v>
+      </c>
+      <c r="I71" t="s">
+        <v>495</v>
+      </c>
+      <c r="J71" t="s">
+        <v>295</v>
+      </c>
+      <c r="K71" t="s">
+        <v>493</v>
+      </c>
+      <c r="L71" t="s">
+        <v>492</v>
+      </c>
+      <c r="M71" t="s">
+        <v>287</v>
+      </c>
+      <c r="N71" t="s">
+        <v>491</v>
+      </c>
+      <c r="O71" t="s">
+        <v>490</v>
+      </c>
+      <c r="P71" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
